--- a/Finance/Budget/Template  Budget 2026.xlsx
+++ b/Finance/Budget/Template  Budget 2026.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\Finance\Budget\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{206E1753-66B0-4248-BDFA-D7A3559D3F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12900BFF-1BDC-44C1-8225-E2B0517334C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{C752B20F-7AE2-4B41-8D8B-727D212FDD9C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{C752B20F-7AE2-4B41-8D8B-727D212FDD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Head" sheetId="4" r:id="rId1"/>
     <sheet name="Line1" sheetId="3" r:id="rId2"/>
     <sheet name="Line2" sheetId="2" r:id="rId3"/>
     <sheet name="Description" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="114210"/>
 </workbook>
@@ -36,6 +37,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Description: SCN Counter_x000D_
 Type: string_x000D_
@@ -137,6 +139,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Instance_x000D_
 Type: long_x000D_
@@ -154,6 +157,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>This field serves as the key of the record in SAP BusinessOne system and it is mandatory. This field is used as a reference in the child template. When adding new data, the value of this field should be user defined (e.g., 1,2,3, etc.). When updating existing data, the value of this field should be the real record key in SAP BusinessOne.</t>
         </r>
@@ -177,6 +181,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Row Number_x000D_
 Type: long_x000D_
@@ -193,6 +198,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Monthly Budget - SC Deb._x000D_
 Type: double_x000D_
@@ -209,6 +215,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Monthly Bal. - Deb._x000D_
 Type: double_x000D_
@@ -225,6 +232,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Monthly Budget - SC Cr._x000D_
 Type: double_x000D_
@@ -241,6 +249,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Monthly Bal. - Cr._x000D_
 Type: double_x000D_
@@ -257,6 +266,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>This field serves as a link to the parent template and it is mandatory. Either when adding new data or updating existing data, the value of this field should be taken from the parent template (the value of the first field in the parent template). The name of the parent key field is specified in the second row of this template.</t>
         </r>
@@ -423,6 +433,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Description: SCN Counter_x000D_
 Type: string_x000D_
@@ -524,6 +535,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Instance_x000D_
 Type: long_x000D_
@@ -541,6 +553,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>This field serves as the key of the record in SAP BusinessOne system and it is mandatory. This field is used as a reference in the child template. When adding new data, the value of this field should be user defined (e.g., 1,2,3, etc.). When updating existing data, the value of this field should be the real record key in SAP BusinessOne.</t>
         </r>
@@ -554,6 +567,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Row Number_x000D_
 Type: long_x000D_
@@ -570,6 +584,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Monthly Budget - SC Deb._x000D_
 Type: double_x000D_
@@ -586,6 +601,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Monthly Bal. - Deb._x000D_
 Type: double_x000D_
@@ -602,6 +618,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Monthly Budget - SC Cr._x000D_
 Type: double_x000D_
@@ -618,6 +635,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Monthly Bal. - Cr._x000D_
 Type: double_x000D_
@@ -634,6 +652,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Instance_x000D_
 Type: long_x000D_
@@ -651,6 +670,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>This field serves as a link to the parent template and it is mandatory. Either when adding new data or updating existing data, the value of this field should be taken from the parent template (the value of the first field in the parent template). The name of the parent key field is specified in the second row of this template.</t>
         </r>
@@ -782,6 +802,7 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Description: Instance_x000D_
 Type: long_x000D_
@@ -810,7 +831,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="226">
   <si>
     <t>Numerator</t>
   </si>
@@ -957,13 +978,548 @@
   </si>
   <si>
     <t>Line2</t>
+  </si>
+  <si>
+    <t>Accounting and Finance</t>
+  </si>
+  <si>
+    <t>Audit fee</t>
+  </si>
+  <si>
+    <t>Bank services and similar charges</t>
+  </si>
+  <si>
+    <t>Entertainment expense - Accounting and Finance</t>
+  </si>
+  <si>
+    <t>625.03.06</t>
+  </si>
+  <si>
+    <t>Licence Fee - Others</t>
+  </si>
+  <si>
+    <t>Miscelleneous expenses - Accounting and Finance</t>
+  </si>
+  <si>
+    <t>668.04.06</t>
+  </si>
+  <si>
+    <t>Other Tax Obligation</t>
+  </si>
+  <si>
+    <t>Present and Gift expenses - Accounting and Finance</t>
+  </si>
+  <si>
+    <t>625.04.06</t>
+  </si>
+  <si>
+    <t>Stamp &amp; Duty</t>
+  </si>
+  <si>
+    <t>Training - Others</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>Cleaning Service</t>
+  </si>
+  <si>
+    <t>Electric Charge for ( LPB )</t>
+  </si>
+  <si>
+    <t>606.06.02</t>
+  </si>
+  <si>
+    <t>Electric Charge for ( Pakse )</t>
+  </si>
+  <si>
+    <t>606.06.04</t>
+  </si>
+  <si>
+    <t>Electric Charge for ( SVK  )</t>
+  </si>
+  <si>
+    <t>606.06.03</t>
+  </si>
+  <si>
+    <t>Entertainment expense - Administration</t>
+  </si>
+  <si>
+    <t>625.03.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet Service Expenses </t>
+  </si>
+  <si>
+    <t>IT Expenses - others</t>
+  </si>
+  <si>
+    <t>Maintenance - IT Hardware &amp; Software</t>
+  </si>
+  <si>
+    <t>Miscelleneous expenses - Administration</t>
+  </si>
+  <si>
+    <t>Office supplies</t>
+  </si>
+  <si>
+    <t>Other Expenses - Vehicles</t>
+  </si>
+  <si>
+    <t>Petrol Expense - ( HQ )</t>
+  </si>
+  <si>
+    <t>606.08.01</t>
+  </si>
+  <si>
+    <t>Petrol Expense - ( LPB )</t>
+  </si>
+  <si>
+    <t>606.08.02</t>
+  </si>
+  <si>
+    <t>Present and Gift expenses - Administration</t>
+  </si>
+  <si>
+    <t>625.04.08</t>
+  </si>
+  <si>
+    <t>Printing and Stationary expenses</t>
+  </si>
+  <si>
+    <t>Rental information technology</t>
+  </si>
+  <si>
+    <t>Rental office  - ( HQ )</t>
+  </si>
+  <si>
+    <t>612.01.01</t>
+  </si>
+  <si>
+    <t>Rental office  - ( LPB )</t>
+  </si>
+  <si>
+    <t>612.01.02</t>
+  </si>
+  <si>
+    <t>Rental office  - ( PAKSE )</t>
+  </si>
+  <si>
+    <t>612.01.04</t>
+  </si>
+  <si>
+    <t>Rental office  - ( SVK )</t>
+  </si>
+  <si>
+    <t>612.01.03</t>
+  </si>
+  <si>
+    <t>Rental Printer - ( HQ )</t>
+  </si>
+  <si>
+    <t>612.02.01</t>
+  </si>
+  <si>
+    <t>Repair &amp; Maintenance Expense - Building &amp; Infrastructure</t>
+  </si>
+  <si>
+    <t>Repair &amp; Maintenance Expense - Vehicles</t>
+  </si>
+  <si>
+    <t>Security Service</t>
+  </si>
+  <si>
+    <t>SMS Service Expenses</t>
+  </si>
+  <si>
+    <t>Telephone Expenses</t>
+  </si>
+  <si>
+    <t>Transport - Local</t>
+  </si>
+  <si>
+    <t>Transport - Oversea</t>
+  </si>
+  <si>
+    <t>Vehicle Insurance</t>
+  </si>
+  <si>
+    <t>Water supply for - ( LPB )</t>
+  </si>
+  <si>
+    <t>606.07.02</t>
+  </si>
+  <si>
+    <t>Water supply for - ( PAKSE )</t>
+  </si>
+  <si>
+    <t>606.07.04</t>
+  </si>
+  <si>
+    <t>Water supply for - ( SVK )</t>
+  </si>
+  <si>
+    <t>606.07.03</t>
+  </si>
+  <si>
+    <t>Compliance &amp; Legal</t>
+  </si>
+  <si>
+    <t>Member of the Insurance Association - Local</t>
+  </si>
+  <si>
+    <t>Miscelleneous expenses - Compliance &amp; Legal</t>
+  </si>
+  <si>
+    <t>668.04.09</t>
+  </si>
+  <si>
+    <t>Other Service Fee</t>
+  </si>
+  <si>
+    <t>Present and Gift expenses - Compliance &amp; Legal</t>
+  </si>
+  <si>
+    <t>625.04.09</t>
+  </si>
+  <si>
+    <t>General Claims</t>
+  </si>
+  <si>
+    <t>Domestic Travel Expense - Claims - Motor</t>
+  </si>
+  <si>
+    <t>625.01.04</t>
+  </si>
+  <si>
+    <t>Entertainment expense - Claims - Motor</t>
+  </si>
+  <si>
+    <t>625.03.01</t>
+  </si>
+  <si>
+    <t>Miscelleneous expenses - Claims - Motor</t>
+  </si>
+  <si>
+    <t>668.04.04</t>
+  </si>
+  <si>
+    <t>Sociality</t>
+  </si>
+  <si>
+    <t>Health Claims</t>
+  </si>
+  <si>
+    <t>Consultant fee</t>
+  </si>
+  <si>
+    <t>Domestic Travel Expense - Claims - Health</t>
+  </si>
+  <si>
+    <t>625.01.05</t>
+  </si>
+  <si>
+    <t>Entertainment expense - Claims - Health</t>
+  </si>
+  <si>
+    <t>625.03.05</t>
+  </si>
+  <si>
+    <t>Other Selling Expenses - Advertising</t>
+  </si>
+  <si>
+    <t>Overseas Travel Expense - Claims - Health</t>
+  </si>
+  <si>
+    <t>625.02.05</t>
+  </si>
+  <si>
+    <t>Present and Gift expenses - Claims - Health</t>
+  </si>
+  <si>
+    <t>625.04.05</t>
+  </si>
+  <si>
+    <t>Training - Course/ Trainer</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>Accident and Health Insurance</t>
+  </si>
+  <si>
+    <t>Advertising, publications, printing public relations fees</t>
+  </si>
+  <si>
+    <t>Bonuses - Management &amp; Staff - Accounting and Finance</t>
+  </si>
+  <si>
+    <t>Bonuses - Management &amp; Staff - Claims - Health</t>
+  </si>
+  <si>
+    <t>Bonuses - Management &amp; Staff - Claims - Motor</t>
+  </si>
+  <si>
+    <t>Bonuses - Management &amp; Staff - Compliance &amp; Legal</t>
+  </si>
+  <si>
+    <t>Bonuses - Management &amp; Staff - HR/Payroll</t>
+  </si>
+  <si>
+    <t>Bonuses - Management &amp; Staff - Management</t>
+  </si>
+  <si>
+    <t>Bonuses - Management &amp; Staff - Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Bonuses - Management &amp; Staff - Underwriting</t>
+  </si>
+  <si>
+    <t>Domestic Travel Expense - HR/Payroll</t>
+  </si>
+  <si>
+    <t>625.01.07</t>
+  </si>
+  <si>
+    <t>Entertainment expense - HR/Payroll</t>
+  </si>
+  <si>
+    <t>625.03.07</t>
+  </si>
+  <si>
+    <t>Overseas Travel Expense - Management</t>
+  </si>
+  <si>
+    <t>625.02.01</t>
+  </si>
+  <si>
+    <t>Position allowance - Management &amp; Staff - Accounting and Finance</t>
+  </si>
+  <si>
+    <t>636.01.06</t>
+  </si>
+  <si>
+    <t>Position allowance - Management &amp; Staff - Claims - Health</t>
+  </si>
+  <si>
+    <t>636.01.05</t>
+  </si>
+  <si>
+    <t>Position allowance - Management &amp; Staff - Claims - Motor</t>
+  </si>
+  <si>
+    <t>636.01.04</t>
+  </si>
+  <si>
+    <t>Position allowance - Management &amp; Staff - Compliance &amp; Legal</t>
+  </si>
+  <si>
+    <t>636.01.09</t>
+  </si>
+  <si>
+    <t>Position allowance - Management &amp; Staff - HR/Payroll</t>
+  </si>
+  <si>
+    <t>636.01.07</t>
+  </si>
+  <si>
+    <t>Position allowance - Management &amp; Staff - Management</t>
+  </si>
+  <si>
+    <t>636.01.01</t>
+  </si>
+  <si>
+    <t>Position allowance - Management &amp; Staff - Sales and Marketing</t>
+  </si>
+  <si>
+    <t>636.01.02</t>
+  </si>
+  <si>
+    <t>Position allowance - Management &amp; Staff - Underwriting</t>
+  </si>
+  <si>
+    <t>636.01.03</t>
+  </si>
+  <si>
+    <t>Salaries - Management &amp; Staff - Accounting and Finance</t>
+  </si>
+  <si>
+    <t>Salaries - Management &amp; Staff - Claims - Health</t>
+  </si>
+  <si>
+    <t>Salaries - Management &amp; Staff - Claims - Motor</t>
+  </si>
+  <si>
+    <t>Salaries - Management &amp; Staff - Compliance &amp; Legal</t>
+  </si>
+  <si>
+    <t>Salaries - Management &amp; Staff - HR/Payroll</t>
+  </si>
+  <si>
+    <t>Salaries - Management &amp; Staff - Management</t>
+  </si>
+  <si>
+    <t>Salaries - Management &amp; Staff - Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Salaries - Management &amp; Staff - Underwriting</t>
+  </si>
+  <si>
+    <t>Salaries Taxes</t>
+  </si>
+  <si>
+    <t>Social security fund - Management&amp;Staff - Accounting and Finance</t>
+  </si>
+  <si>
+    <t>Social security fund - Management&amp;Staff - Claims - Health</t>
+  </si>
+  <si>
+    <t>Social security fund - Management&amp;Staff - Claims - Motor</t>
+  </si>
+  <si>
+    <t>Social security fund - Management&amp;Staff - Compliance &amp; Legal</t>
+  </si>
+  <si>
+    <t>Social security fund - Management&amp;Staff - HR/Payroll</t>
+  </si>
+  <si>
+    <t>Social security fund - Management&amp;Staff - Management</t>
+  </si>
+  <si>
+    <t>Social security fund - Management&amp;Staff - Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Social security fund - Management&amp;Staff - Underwriting</t>
+  </si>
+  <si>
+    <t>Training - Hotel Accommodation</t>
+  </si>
+  <si>
+    <t>Training - Travelling Expenses</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Domestic Travel Expense - Management</t>
+  </si>
+  <si>
+    <t>625.01.01</t>
+  </si>
+  <si>
+    <t>Entertainment expense - Management</t>
+  </si>
+  <si>
+    <t>Sales and Marketing CPS</t>
+  </si>
+  <si>
+    <t>Domestic Travel Expense - Sales and Marketing</t>
+  </si>
+  <si>
+    <t>625.01.02</t>
+  </si>
+  <si>
+    <t>Entertainment expense - Sales and Marketing</t>
+  </si>
+  <si>
+    <t>625.03.02</t>
+  </si>
+  <si>
+    <t>Petrol Expense - ( PAKSE )</t>
+  </si>
+  <si>
+    <t>606.08.04</t>
+  </si>
+  <si>
+    <t>Present and Gift expenses - Sales and Marketing</t>
+  </si>
+  <si>
+    <t>625.04.02</t>
+  </si>
+  <si>
+    <t>Sales and Marketing HQ</t>
+  </si>
+  <si>
+    <t>Other Selling Expenses - Others</t>
+  </si>
+  <si>
+    <t>Other Selling Expenses - Promotion</t>
+  </si>
+  <si>
+    <t>Sales and Marketing LPB</t>
+  </si>
+  <si>
+    <t>Internet Service Expenses</t>
+  </si>
+  <si>
+    <t>Underwriting</t>
+  </si>
+  <si>
+    <t>Domestic Travel Expense - Underwriting</t>
+  </si>
+  <si>
+    <t>625.01.03</t>
+  </si>
+  <si>
+    <t>Entertainment expense - Underwriting</t>
+  </si>
+  <si>
+    <t>625.03.03</t>
+  </si>
+  <si>
+    <t>Overseas Travel Expense - Underwriting</t>
+  </si>
+  <si>
+    <t>625.02.03</t>
+  </si>
+  <si>
+    <t>Present and Gift expenses - Underwriting</t>
+  </si>
+  <si>
+    <t>625.04.03</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>C02.03</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General  Claims </t>
+  </si>
+  <si>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>C07</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>Code of Department</t>
+  </si>
+  <si>
+    <t>Name of Department</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="187" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -974,18 +1530,19 @@
       <u/>
       <sz val="9"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -998,13 +1555,6 @@
       <b/>
       <sz val="9"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
@@ -1074,8 +1624,26 @@
       <color theme="1"/>
       <name val="Phetsarath OT"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1112,8 +1680,50 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1121,31 +1731,85 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="187" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1766,7 +2430,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1786,7 +2450,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1806,7 +2470,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -1826,7 +2490,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -2235,4 +2899,2409 @@
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6FAA53-6F05-493E-9E72-A874A233A2B3}">
+  <dimension ref="A1:J144"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="1" width="58.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="13.8">
+      <c r="A1" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="19">
+        <v>432620000</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="22">
+        <v>264000000</v>
+      </c>
+      <c r="C2" s="23">
+        <v>628.03</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="22">
+        <v>100000000</v>
+      </c>
+      <c r="C3" s="23">
+        <v>627.01</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="22">
+        <v>6000000</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="25">
+        <v>20000000</v>
+      </c>
+      <c r="C5" s="26">
+        <v>648.08000000000004</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="22">
+        <v>2520000</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="22">
+        <v>10000000</v>
+      </c>
+      <c r="C7" s="20">
+        <v>648.05999999999995</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="22">
+        <v>2500000</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="22">
+        <v>3600000</v>
+      </c>
+      <c r="C9" s="27">
+        <v>647.01</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="22">
+        <v>24000000</v>
+      </c>
+      <c r="C10" s="20">
+        <v>626.04</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="13.8">
+      <c r="A11" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="19">
+        <v>2425178616</v>
+      </c>
+      <c r="C11" s="20"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="22">
+        <v>24240000</v>
+      </c>
+      <c r="C12" s="26">
+        <v>628.02</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="22">
+        <v>6000000</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="22">
+        <v>12000000</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="22">
+        <v>6000000</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="22">
+        <v>383600000</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="22">
+        <v>34440000</v>
+      </c>
+      <c r="C17" s="27">
+        <v>623.02</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="22">
+        <v>10000000</v>
+      </c>
+      <c r="C18" s="26">
+        <v>606.04</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="22">
+        <v>52362000</v>
+      </c>
+      <c r="C19" s="26">
+        <v>614.03</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="22">
+        <v>3600000</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="22">
+        <v>60450000</v>
+      </c>
+      <c r="C21" s="26">
+        <v>606.01</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="22">
+        <v>20880000</v>
+      </c>
+      <c r="C22" s="26">
+        <v>606.04999999999995</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="22">
+        <v>180000000</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="22">
+        <v>4800000</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="22">
+        <v>3600000</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="22">
+        <v>96000000</v>
+      </c>
+      <c r="C26" s="26">
+        <v>606.02</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="22">
+        <v>441833016</v>
+      </c>
+      <c r="C27" s="28">
+        <v>612.04</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="22">
+        <v>551073600</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="22">
+        <v>84000000</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="22">
+        <v>30000000</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="22">
+        <v>48000000</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="22">
+        <v>120000000</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="22">
+        <v>30000000</v>
+      </c>
+      <c r="C33" s="26">
+        <v>614.01</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="22">
+        <v>104400000</v>
+      </c>
+      <c r="C34" s="26">
+        <v>614.04</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="22">
+        <v>19200000</v>
+      </c>
+      <c r="C35" s="26">
+        <v>628.01</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="22">
+        <v>8400000</v>
+      </c>
+      <c r="C36" s="26">
+        <v>623.03</v>
+      </c>
+      <c r="D36" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="22">
+        <v>1800000</v>
+      </c>
+      <c r="C37" s="26">
+        <v>647.01</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="22">
+        <v>18000000</v>
+      </c>
+      <c r="C38" s="26">
+        <v>623.01</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="22">
+        <v>6000000</v>
+      </c>
+      <c r="C39" s="26">
+        <v>621.01</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B40" s="22">
+        <v>6900000</v>
+      </c>
+      <c r="C40" s="26">
+        <v>621.02</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="22">
+        <v>36000000</v>
+      </c>
+      <c r="C41" s="27">
+        <v>615.02</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42" s="22">
+        <v>7200000</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" s="22">
+        <v>7200000</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B44" s="22">
+        <v>7200000</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="13.8">
+      <c r="A45" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" s="19">
+        <v>99900000</v>
+      </c>
+      <c r="C45" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="22">
+        <v>7500000</v>
+      </c>
+      <c r="C46" s="26">
+        <v>648.08000000000004</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" s="22">
+        <v>24400000</v>
+      </c>
+      <c r="C47" s="26">
+        <v>617.02</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="E47" s="33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B48" s="25">
+        <v>25000000</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" s="22">
+        <v>30000000</v>
+      </c>
+      <c r="C49" s="26">
+        <v>628.04999999999995</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="E49" s="33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="22">
+        <v>1000000</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="E50" s="33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="22">
+        <v>12000000</v>
+      </c>
+      <c r="C51" s="26">
+        <v>626.04</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="13.8">
+      <c r="A52" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="19">
+        <v>224500000</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="22">
+        <v>60000000</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="D53" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="22">
+        <v>58000000</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D54" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="22">
+        <v>50000000</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D55" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E55" s="33" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56" s="22">
+        <v>12000000</v>
+      </c>
+      <c r="C56" s="26">
+        <v>606.02</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E56" s="33" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" s="22">
+        <v>14500000</v>
+      </c>
+      <c r="C57" s="26">
+        <v>656.01</v>
+      </c>
+      <c r="D57" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E57" s="33" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="22">
+        <v>30000000</v>
+      </c>
+      <c r="C58" s="26">
+        <v>626.04</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E58" s="33" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="13.8">
+      <c r="A59" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" s="19">
+        <v>99200000</v>
+      </c>
+      <c r="C59" s="31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="22">
+        <v>30000000</v>
+      </c>
+      <c r="C60" s="26">
+        <v>628.04</v>
+      </c>
+      <c r="D60" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E60" s="33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B61" s="22">
+        <v>12000000</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D61" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E61" s="33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" s="22">
+        <v>14000000</v>
+      </c>
+      <c r="C62" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D62" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E62" s="33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B63" s="22">
+        <v>6000000</v>
+      </c>
+      <c r="C63" s="26">
+        <v>622.01</v>
+      </c>
+      <c r="D63" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E63" s="33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" s="22">
+        <v>10000000</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D64" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64" s="33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B65" s="22">
+        <v>8000000</v>
+      </c>
+      <c r="C65" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B66" s="22">
+        <v>12000000</v>
+      </c>
+      <c r="C66" s="26">
+        <v>626.01</v>
+      </c>
+      <c r="D66" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B67" s="22">
+        <v>6000000</v>
+      </c>
+      <c r="C67" s="26">
+        <v>621.01</v>
+      </c>
+      <c r="D67" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B68" s="22">
+        <v>1200000</v>
+      </c>
+      <c r="C68" s="26">
+        <v>621.02</v>
+      </c>
+      <c r="D68" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="13.8">
+      <c r="A69" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" s="19">
+        <v>14267501523.25</v>
+      </c>
+      <c r="C69" s="31" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" s="22">
+        <v>110000000</v>
+      </c>
+      <c r="C70" s="26">
+        <v>615.03</v>
+      </c>
+      <c r="D70" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E70" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" s="22">
+        <v>6000000</v>
+      </c>
+      <c r="C71" s="27">
+        <v>622.01</v>
+      </c>
+      <c r="D71" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E71" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B72" s="22">
+        <v>144000000</v>
+      </c>
+      <c r="C72" s="26">
+        <v>632.05999999999995</v>
+      </c>
+      <c r="D72" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E72" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B73" s="22">
+        <v>126734231.25</v>
+      </c>
+      <c r="C73" s="26">
+        <v>632.04999999999995</v>
+      </c>
+      <c r="D73" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E73" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B74" s="22">
+        <v>144000000</v>
+      </c>
+      <c r="C74" s="26">
+        <v>632.04</v>
+      </c>
+      <c r="D74" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E74" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="B75" s="22">
+        <v>72000000</v>
+      </c>
+      <c r="C75" s="26">
+        <v>632.09</v>
+      </c>
+      <c r="D75" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E75" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B76" s="22">
+        <v>132000000</v>
+      </c>
+      <c r="C76" s="26">
+        <v>632.07000000000005</v>
+      </c>
+      <c r="D76" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E76" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="B77" s="22">
+        <v>480000000</v>
+      </c>
+      <c r="C77" s="26">
+        <v>632.01</v>
+      </c>
+      <c r="D77" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E77" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B78" s="22">
+        <v>720000000</v>
+      </c>
+      <c r="C78" s="26">
+        <v>632.02</v>
+      </c>
+      <c r="D78" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E78" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B79" s="22">
+        <v>180000000</v>
+      </c>
+      <c r="C79" s="27">
+        <v>632.03</v>
+      </c>
+      <c r="D79" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E79" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B80" s="22">
+        <v>7500000</v>
+      </c>
+      <c r="C80" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D80" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E80" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B81" s="22">
+        <v>6000000</v>
+      </c>
+      <c r="C81" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="D81" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E81" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B82" s="22">
+        <v>45000000</v>
+      </c>
+      <c r="C82" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="D82" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E82" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B83" s="22">
+        <v>40800000</v>
+      </c>
+      <c r="C83" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="D83" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E83" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B84" s="22">
+        <v>40800000</v>
+      </c>
+      <c r="C84" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="D84" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E84" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B85" s="22">
+        <v>60000000</v>
+      </c>
+      <c r="C85" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="D85" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E85" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B86" s="22">
+        <v>14400000</v>
+      </c>
+      <c r="C86" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="D86" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E86" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B87" s="22">
+        <v>48000000</v>
+      </c>
+      <c r="C87" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="D87" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E87" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B88" s="22">
+        <v>72000000</v>
+      </c>
+      <c r="C88" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="D88" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E88" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B89" s="22">
+        <v>144000000</v>
+      </c>
+      <c r="C89" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="D89" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E89" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="B90" s="22">
+        <v>54000000</v>
+      </c>
+      <c r="C90" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D90" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E90" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B91" s="22">
+        <v>1131372000.0000002</v>
+      </c>
+      <c r="C91" s="26">
+        <v>631.05999999999995</v>
+      </c>
+      <c r="D91" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E91" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B92" s="22">
+        <v>849113100</v>
+      </c>
+      <c r="C92" s="26">
+        <v>631.04999999999995</v>
+      </c>
+      <c r="D92" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E92" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B93" s="22">
+        <v>1020000000</v>
+      </c>
+      <c r="C93" s="26">
+        <v>631.04</v>
+      </c>
+      <c r="D93" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E93" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B94" s="22">
+        <v>407258192</v>
+      </c>
+      <c r="C94" s="26">
+        <v>631.09</v>
+      </c>
+      <c r="D94" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E94" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B95" s="22">
+        <v>1080000000</v>
+      </c>
+      <c r="C95" s="26">
+        <v>631.07000000000005</v>
+      </c>
+      <c r="D95" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E95" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B96" s="22">
+        <v>1920000000</v>
+      </c>
+      <c r="C96" s="26">
+        <v>631.01</v>
+      </c>
+      <c r="D96" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E96" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="B97" s="22">
+        <v>2724000000</v>
+      </c>
+      <c r="C97" s="26">
+        <v>631.02</v>
+      </c>
+      <c r="D97" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E97" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="B98" s="22">
+        <v>1020000000</v>
+      </c>
+      <c r="C98" s="26">
+        <v>631.03</v>
+      </c>
+      <c r="D98" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E98" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="B99" s="22">
+        <v>1260000000</v>
+      </c>
+      <c r="C99" s="26">
+        <v>648.01</v>
+      </c>
+      <c r="D99" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E99" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B100" s="22">
+        <v>19872000</v>
+      </c>
+      <c r="C100" s="26">
+        <v>635.05999999999995</v>
+      </c>
+      <c r="D100" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E100" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B101" s="22">
+        <v>19872000</v>
+      </c>
+      <c r="C101" s="26">
+        <v>635.04999999999995</v>
+      </c>
+      <c r="D101" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E101" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="B102" s="22">
+        <v>24288000</v>
+      </c>
+      <c r="C102" s="26">
+        <v>635.04</v>
+      </c>
+      <c r="D102" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E102" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B103" s="22">
+        <v>6624000</v>
+      </c>
+      <c r="C103" s="26">
+        <v>635.09</v>
+      </c>
+      <c r="D103" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E103" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B104" s="22">
+        <v>17664000</v>
+      </c>
+      <c r="C104" s="26">
+        <v>635.07000000000005</v>
+      </c>
+      <c r="D104" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E104" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B105" s="22">
+        <v>8832000</v>
+      </c>
+      <c r="C105" s="26">
+        <v>635.01</v>
+      </c>
+      <c r="D105" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E105" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B106" s="22">
+        <v>36000000</v>
+      </c>
+      <c r="C106" s="26">
+        <v>635.02</v>
+      </c>
+      <c r="D106" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E106" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B107" s="22">
+        <v>19872000</v>
+      </c>
+      <c r="C107" s="26">
+        <v>635.03</v>
+      </c>
+      <c r="D107" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E107" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B108" s="22">
+        <v>31500000</v>
+      </c>
+      <c r="C108" s="26">
+        <v>626.01</v>
+      </c>
+      <c r="D108" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E108" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="B109" s="22">
+        <v>12000000</v>
+      </c>
+      <c r="C109" s="26">
+        <v>626.02</v>
+      </c>
+      <c r="D109" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E109" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B110" s="22">
+        <v>7000000</v>
+      </c>
+      <c r="C110" s="26">
+        <v>626.04</v>
+      </c>
+      <c r="D110" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E110" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B111" s="22">
+        <v>5000000</v>
+      </c>
+      <c r="C111" s="26">
+        <v>626.03</v>
+      </c>
+      <c r="D111" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E111" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="13.8">
+      <c r="A112" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="B112" s="19">
+        <v>361380000</v>
+      </c>
+      <c r="C112" s="31" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B113" s="22">
+        <v>51500000</v>
+      </c>
+      <c r="C113" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="D113" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="E113" s="33" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B114" s="22">
+        <v>79000000</v>
+      </c>
+      <c r="C114" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D114" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="E114" s="33" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B115" s="22">
+        <v>230880000</v>
+      </c>
+      <c r="C115" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="D115" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="E115" s="33" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="13.8">
+      <c r="A116" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B116" s="19">
+        <v>59000000</v>
+      </c>
+      <c r="C116" s="31" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="B117" s="22">
+        <v>22800000</v>
+      </c>
+      <c r="C117" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="D117" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="E117" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B118" s="22">
+        <v>27000000</v>
+      </c>
+      <c r="C118" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D118" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="E118" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="I118" s="32"/>
+      <c r="J118" s="33"/>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B119" s="22">
+        <v>4200000</v>
+      </c>
+      <c r="C119" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="D119" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="E119" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="B120" s="22">
+        <v>5000000</v>
+      </c>
+      <c r="C120" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="D120" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="E120" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="13.8">
+      <c r="A121" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B121" s="19">
+        <v>972400000</v>
+      </c>
+      <c r="C121" s="31" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="B122" s="22">
+        <v>180000000</v>
+      </c>
+      <c r="C122" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="D122" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E122" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B123" s="22">
+        <v>55200000</v>
+      </c>
+      <c r="C123" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D123" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E123" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="I123" s="32"/>
+      <c r="J123" s="33"/>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B124" s="25">
+        <v>49700000</v>
+      </c>
+      <c r="C124" s="27">
+        <v>648.08000000000004</v>
+      </c>
+      <c r="D124" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E124" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" s="22">
+        <v>190200000</v>
+      </c>
+      <c r="C125" s="26">
+        <v>622.01</v>
+      </c>
+      <c r="D125" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E125" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B126" s="22">
+        <v>96200000</v>
+      </c>
+      <c r="C126" s="27">
+        <v>622.03</v>
+      </c>
+      <c r="D126" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E126" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B127" s="22">
+        <v>229500000</v>
+      </c>
+      <c r="C127" s="27">
+        <v>622.02</v>
+      </c>
+      <c r="D127" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E127" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="B128" s="22">
+        <v>125000000</v>
+      </c>
+      <c r="C128" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D128" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E128" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B129" s="22">
+        <v>8000000</v>
+      </c>
+      <c r="C129" s="26">
+        <v>623.03</v>
+      </c>
+      <c r="D129" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E129" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B130" s="22">
+        <v>35000000</v>
+      </c>
+      <c r="C130" s="26">
+        <v>656.01</v>
+      </c>
+      <c r="D130" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E130" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B131" s="22">
+        <v>3600000</v>
+      </c>
+      <c r="C131" s="27">
+        <v>621.01</v>
+      </c>
+      <c r="D131" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E131" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="13.8">
+      <c r="A132" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B132" s="19">
+        <v>32460000</v>
+      </c>
+      <c r="C132" s="31" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="B133" s="22">
+        <v>12000000</v>
+      </c>
+      <c r="C133" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="D133" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E133" s="33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B134" s="22">
+        <v>1200000</v>
+      </c>
+      <c r="C134" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D134" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E134" s="33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="B135" s="22">
+        <v>3060000</v>
+      </c>
+      <c r="C135" s="26">
+        <v>623.02</v>
+      </c>
+      <c r="D135" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E135" s="33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B136" s="22">
+        <v>10000000</v>
+      </c>
+      <c r="C136" s="26">
+        <v>622.01</v>
+      </c>
+      <c r="D136" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E136" s="33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="B137" s="22">
+        <v>5000000</v>
+      </c>
+      <c r="C137" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="D137" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E137" s="33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B138" s="22">
+        <v>1200000</v>
+      </c>
+      <c r="C138" s="26">
+        <v>621.01</v>
+      </c>
+      <c r="D138" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E138" s="33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="13.8">
+      <c r="A139" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B139" s="19">
+        <v>526300000</v>
+      </c>
+      <c r="C139" s="31" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B140" s="22">
+        <v>170000000</v>
+      </c>
+      <c r="C140" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="D140" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="E140" s="33" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="B141" s="22">
+        <v>10000000</v>
+      </c>
+      <c r="C141" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="D141" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="E141" s="33" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B142" s="22">
+        <v>236300000</v>
+      </c>
+      <c r="C142" s="26">
+        <v>606.01</v>
+      </c>
+      <c r="D142" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="E142" s="33" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B143" s="22">
+        <v>100000000</v>
+      </c>
+      <c r="C143" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="D143" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="E143" s="33" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="B144" s="22">
+        <v>10000000</v>
+      </c>
+      <c r="C144" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="D144" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="E144" s="33" t="s">
+        <v>207</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>